--- a/data/trans_orig/IP31KM10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM10_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14556</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10435</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19085</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12234</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8135</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17514</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>26262</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22879</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18350</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27000</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>49,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>34261</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28981</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38360</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>46478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>59326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>87741</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>76933</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>96174</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>81321</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>71188</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>92623</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>51,05%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100914</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110353</t>
+          <t>81514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>182236</t>
+          <t>159675</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167255</t>
+          <t>145350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197156</t>
+          <t>172381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77978</t>
+          <t>69301</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66676</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88111</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>81045</t>
+          <t>73584</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71606</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93295</t>
+          <t>82812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>159023</t>
+          <t>142885</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144103</t>
+          <t>130179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174004</t>
+          <t>157210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>111217</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>97945</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>124299</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98127</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85481</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>108659</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>116917</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103245</t>
+          <t>88444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131941</t>
+          <t>110618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>215044</t>
+          <t>211666</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198638</t>
+          <t>194752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234243</t>
+          <t>228916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>61,08%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88909</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75827</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>102181</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>74945</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64413</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>87591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>74223</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80549</t>
+          <t>64054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109245</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>170519</t>
+          <t>163132</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151320</t>
+          <t>145882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186925</t>
+          <t>180046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>183449</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>166593</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>201296</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>150707</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>129735</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>187929</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>54,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>185807</t>
+          <t>132693</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165903</t>
+          <t>118391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205163</t>
+          <t>146953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>336514</t>
+          <t>316143</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308413</t>
+          <t>293589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>379826</t>
+          <t>339017</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>108772</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90925</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>123560</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86338</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144532</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>119192</t>
+          <t>122644</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99836</t>
+          <t>108384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139096</t>
+          <t>136946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>242752</t>
+          <t>231415</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199440</t>
+          <t>208541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270853</t>
+          <t>253969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>396963</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>372106</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>422138</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>342390</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>317176</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>383688</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>394361</t>
+          <t>296244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>449275</t>
+          <t>339309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>762210</t>
+          <t>713745</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726618</t>
+          <t>683147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>811629</t>
+          <t>746073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>289861</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>264686</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>314718</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>310744</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>269446</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>335958</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>324913</t>
+          <t>301426</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>295458</t>
+          <t>278899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>350372</t>
+          <t>321964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>635657</t>
+          <t>591286</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>586238</t>
+          <t>558958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>671249</t>
+          <t>621884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
